--- a/data/2026/cjsl/fall/soccer-fun-for-kids-brooklyn-patriots-2015-2016.xlsx
+++ b/data/2026/cjsl/fall/soccer-fun-for-kids-brooklyn-patriots-2015-2016.xlsx
@@ -214,7 +214,7 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rained Out</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/soccer-fun-for-kids-brooklyn-patriots-2015-2016.xlsx
+++ b/data/2026/cjsl/fall/soccer-fun-for-kids-brooklyn-patriots-2015-2016.xlsx
@@ -239,7 +239,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4 - 0</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/soccer-fun-for-kids-brooklyn-patriots-2015-2016.xlsx
+++ b/data/2026/cjsl/fall/soccer-fun-for-kids-brooklyn-patriots-2015-2016.xlsx
@@ -284,7 +284,7 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2 - 4</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/soccer-fun-for-kids-brooklyn-patriots-2015-2016.xlsx
+++ b/data/2026/cjsl/fall/soccer-fun-for-kids-brooklyn-patriots-2015-2016.xlsx
@@ -78,7 +78,7 @@
     <col min="6" max="6" bestFit="1" customWidth="1" width="46.2"/>
     <col min="7" max="7" bestFit="1" customWidth="1" width="49.50000000000001"/>
     <col min="8" max="8" bestFit="1" customWidth="1" width="18.700000000000003"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" width="11.0"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" width="12.100000000000001"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -175,36 +175,36 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="n">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>Sunday, September 27, 2026</t>
+          <t>Sunday, October  4, 2026</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>11:00 EDT</t>
+          <t>14:20 EDT</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>Soccer Fun for Kids / Brooklyn Patriots 2015-2016</t>
+          <t>South Brooklyn Fc 2015/2016</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4 - 0</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>Stage10 FC Boys Leopards 2015/2016</t>
+          <t>Soccer Fun for Kids / Brooklyn Patriots 2015-2016</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>Prospect Park, Parade Grounds Field 7A - Parade Grounds Field 7A</t>
+          <t>Bush Terminal Park - Bush Terminal #2 11v11</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
@@ -214,42 +214,42 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>Rained Out</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>Sunday, October  4, 2026</t>
+          <t>Sunday, October 18, 2026</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>14:20 EDT</t>
+          <t>11:00 EDT</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>South Brooklyn Fc 2015/2016</t>
+          <t>Soccer Fun for Kids / Brooklyn Patriots 2015-2016</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>4 - 0</t>
+          <t>2 - 4</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>Soccer Fun for Kids / Brooklyn Patriots 2015-2016</t>
+          <t>Brooklyn City FC F.C. B15/16 Blue</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>Bush Terminal Park - Bush Terminal #2 11v11</t>
+          <t>Prospect Park, Parade Grounds Field 7A - Parade Grounds Field 7A</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
@@ -265,36 +265,36 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="n">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>Sunday, October 18, 2026</t>
+          <t>Saturday, October 24, 2026</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>11:00 EDT</t>
+          <t>08:15 EDT</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>Soccer Fun for Kids / Brooklyn Patriots 2015-2016</t>
+          <t>ALBION SC Brooklyn B15/16 Premier - Williamsburg</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>2 - 4</t>
+          <t>4 - 4</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>Brooklyn City FC F.C. B15/16 Blue</t>
+          <t>Soccer Fun for Kids / Brooklyn Patriots 2015-2016</t>
         </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>Prospect Park, Parade Grounds Field 7A - Parade Grounds Field 7A</t>
+          <t>Frank Principe Park/ Maurice Park Soccer 04  - Field 4</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
@@ -310,21 +310,21 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="n">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October 24, 2026</t>
+          <t>Saturday, October 31, 2026</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>08:15 EDT</t>
+          <t>10:00 EDT</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>ALBION SC Brooklyn B15/16 Premier - Williamsburg</t>
+          <t>Stage10 FC Boys Leopards 2015/2016</t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr">
@@ -339,7 +339,7 @@
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>Frank Principe Park/ Maurice Park Soccer 04  - Field 4</t>
+          <t>Randall's Island - 7</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
@@ -349,27 +349,27 @@
       </c>
       <c r="I6" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="n">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October 31, 2026</t>
+          <t>Sunday, November  8, 2026</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>10:00 EDT</t>
+          <t>11:00 EST</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>Stage10 FC Boys Leopards 2015/2016</t>
+          <t>Soccer Fun for Kids / Brooklyn Patriots 2015-2016</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
@@ -379,12 +379,12 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>Soccer Fun for Kids / Brooklyn Patriots 2015-2016</t>
+          <t>South Brooklyn Fc 2015/2016</t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>Randall's Island - 7</t>
+          <t>Prospect Park, Parade Grounds Field 7A - Parade Grounds Field 7A</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
@@ -394,27 +394,27 @@
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="n">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>Sunday, November  8, 2026</t>
+          <t>Saturday, November 14, 2026</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>11:00 EST</t>
+          <t>15:00 EST</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t>Soccer Fun for Kids / Brooklyn Patriots 2015-2016</t>
+          <t>Brooklyn City FC F.C. B15/16 Blue</t>
         </is>
       </c>
       <c r="E8" s="0" t="inlineStr">
@@ -424,12 +424,12 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>South Brooklyn Fc 2015/2016</t>
+          <t>Soccer Fun for Kids / Brooklyn Patriots 2015-2016</t>
         </is>
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>Prospect Park, Parade Grounds Field 7A - Parade Grounds Field 7A</t>
+          <t>Bush Terminal Piers Park - Soccer 03 (Back field)</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
@@ -445,21 +445,21 @@
     </row>
     <row r="9">
       <c r="A9" s="0" t="n">
-        <v>531</v>
+        <v>512</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>Saturday, November 14, 2026</t>
+          <t>Sunday, November 15, 2026</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>15:00 EST</t>
+          <t>11:00 EST</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t>Brooklyn City FC F.C. B15/16 Blue</t>
+          <t>Soccer Fun for Kids / Brooklyn Patriots 2015-2016</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
@@ -469,12 +469,12 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>Soccer Fun for Kids / Brooklyn Patriots 2015-2016</t>
+          <t>Stage10 FC Boys Leopards 2015/2016</t>
         </is>
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>Bush Terminal Piers Park - Soccer 03 (Back field)</t>
+          <t>Prospect Park, Parade Grounds Field 7A - Parade Grounds Field 7A</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
@@ -484,7 +484,7 @@
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rescheduled</t>
         </is>
       </c>
     </row>
